--- a/BiblioParsing/BiblioParsing_RefFiles/Institute_affiliations.xlsx
+++ b/BiblioParsing/BiblioParsing_RefFiles/Institute_affiliations.xlsx
@@ -1,33 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AC265100\BiblioParsing_Files\Parametres Institut\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AC265100\Documents\BiblioMeter_App\LETI\Bibliometry\BiblioMeter_Files-6.2.0\Traitement Institutions\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D60A8BF5-83B1-4685-BDE0-D9EFFBB60F4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14100" windowHeight="6015"/>
+    <workbookView xWindow="-21100" yWindow="5200" windowWidth="20820" windowHeight="7050" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="France" sheetId="1" r:id="rId1"/>
+    <sheet name="New" sheetId="3" r:id="rId2"/>
+    <sheet name="unknown" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">France!$A$1:$M$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">France!$A$1:$M$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">unknown!$A$1:$M$5</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="83">
   <si>
     <t>Norm affiliations</t>
   </si>
@@ -95,9 +102,6 @@
     <t>III V Laboratory</t>
   </si>
   <si>
-    <t>Laboratoire de Physique des 2 Infinis Irène Joliot-Curie</t>
-  </si>
-  <si>
     <t>LETI Inst</t>
   </si>
   <si>
@@ -113,9 +117,6 @@
     <t>UMR 5129</t>
   </si>
   <si>
-    <t>Laboratoire Technol Modules Photovoltaiques</t>
-  </si>
-  <si>
     <t>STMicroelectronics Firm</t>
   </si>
   <si>
@@ -138,13 +139,157 @@
   </si>
   <si>
     <t>STMicroelectron</t>
+  </si>
+  <si>
+    <t>CEA/LETI</t>
+  </si>
+  <si>
+    <t>CEA-LETI</t>
+  </si>
+  <si>
+    <t>Laboratoire d'Electronique des Technologies de l'Information</t>
+  </si>
+  <si>
+    <t>CEA LETIMinatec</t>
+  </si>
+  <si>
+    <t>CEA/LETIMinatec</t>
+  </si>
+  <si>
+    <t>CEALETI</t>
+  </si>
+  <si>
+    <t>Laboratoire dElectronique et de Technologies de lInformation</t>
+  </si>
+  <si>
+    <t>Lab Elect Technol Informat</t>
+  </si>
+  <si>
+    <t>Electronic Laboratory of Information Technology</t>
+  </si>
+  <si>
+    <t>Laboratory of Electronics and Information Technologies</t>
+  </si>
+  <si>
+    <t>Lab Technol &amp; Microelect</t>
+  </si>
+  <si>
+    <t>Laboratory of Technologies of Microelectronics</t>
+  </si>
+  <si>
+    <t>Laboratoire des Technologies de la Microelectronique</t>
+  </si>
+  <si>
+    <t>Lab Technol Microelect</t>
+  </si>
+  <si>
+    <t>STMI Croelectronics</t>
+  </si>
+  <si>
+    <t>III/V Lab</t>
+  </si>
+  <si>
+    <t>III-V Laboratory</t>
+  </si>
+  <si>
+    <t>III-Vlab</t>
+  </si>
+  <si>
+    <t>IIIV Lab</t>
+  </si>
+  <si>
+    <t>III-V Joint Lab</t>
+  </si>
+  <si>
+    <t>MINATEC Site</t>
+  </si>
+  <si>
+    <t>MINATEC</t>
+  </si>
+  <si>
+    <t>MINATECH</t>
+  </si>
+  <si>
+    <t>III V lab</t>
+  </si>
+  <si>
+    <t>Microelectronics Technology Laboratory</t>
+  </si>
+  <si>
+    <t>Laboratory delectronique et de technologie de linformation</t>
+  </si>
+  <si>
+    <t>Raw affiliations 13</t>
+  </si>
+  <si>
+    <t>Laboratory 3 5</t>
+  </si>
+  <si>
+    <t>Lab 3 5</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> STMicroelectron</t>
+  </si>
+  <si>
+    <t>ST Micorelectronics</t>
+  </si>
+  <si>
+    <t>LETI Rto</t>
+  </si>
+  <si>
+    <t>LTM CNRS-Lab</t>
+  </si>
+  <si>
+    <t>Joint Lab Nokia Bell Labs Thales Res &amp; Technol</t>
+  </si>
+  <si>
+    <t>LETI-CEATech</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Laboratoire des Technologies de la Microélectronique </t>
+  </si>
+  <si>
+    <t>Laboratory of Technology of Microelectronics</t>
+  </si>
+  <si>
+    <t>Laboratory Technol and Microelect</t>
+  </si>
+  <si>
+    <t>Laboratory d Electronique et de Technologie de l Information</t>
+  </si>
+  <si>
+    <t>Electronics and Information Technology Laboratory</t>
+  </si>
+  <si>
+    <t>Raw affiliations 14</t>
+  </si>
+  <si>
+    <t>Raw affiliations 15</t>
+  </si>
+  <si>
+    <t>Joint Lab Nokia Bell Labs Thales</t>
+  </si>
+  <si>
+    <t>joint lab of Nokia Bell Labs Thales</t>
+  </si>
+  <si>
+    <t>Laboratoire d'Electronique et de Technologie de l'Information</t>
+  </si>
+  <si>
+    <t>Raw affiliations 16</t>
+  </si>
+  <si>
+    <t>Rousset France</t>
+  </si>
+  <si>
+    <t>ST Micorelect</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -158,16 +303,28 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -175,24 +332,135 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="9">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -467,251 +735,685 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr>
+    <tabColor theme="8" tint="0.59999389629810485"/>
+  </sheetPr>
+  <dimension ref="A1:Q8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="29.28515625" style="3" customWidth="1"/>
-    <col min="2" max="2" width="32.140625" customWidth="1"/>
-    <col min="3" max="3" width="72.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="50.7109375" customWidth="1"/>
-    <col min="5" max="5" width="43.7109375" customWidth="1"/>
-    <col min="6" max="6" width="68.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="47.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="59.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="64.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="37.42578125" customWidth="1"/>
-    <col min="11" max="11" width="40" customWidth="1"/>
-    <col min="12" max="12" width="43.7109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="35.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.28515625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="49.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="56" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="36.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="56.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="24.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="44.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="50.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.42578125" customWidth="1"/>
+    <col min="14" max="14" width="54.85546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="55.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="46.5703125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="56.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="N1" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q1" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="6" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="6"/>
+      <c r="N2" s="6"/>
+      <c r="O2" s="6"/>
+      <c r="P2" s="6"/>
+      <c r="Q2" s="6"/>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4"/>
+      <c r="L3" s="4"/>
+      <c r="M3" s="4"/>
+      <c r="N3" s="4"/>
+      <c r="O3" s="4"/>
+      <c r="P3" s="4"/>
+      <c r="Q3" s="4"/>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="H4" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="D4" t="s">
+      <c r="I4" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="K4" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="L4" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="M4" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="N4" s="6"/>
+      <c r="O4" s="6"/>
+      <c r="P4" s="6"/>
+      <c r="Q4" s="6"/>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="L5" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="M5" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="N5" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="O5" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="P5" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q5" s="4" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="K6" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="L6" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="M6" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="N6" s="6"/>
+      <c r="O6" s="6"/>
+      <c r="P6" s="6"/>
+      <c r="Q6" s="6"/>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="4"/>
+      <c r="M7" s="4"/>
+      <c r="N7" s="4"/>
+      <c r="O7" s="4"/>
+      <c r="P7" s="4"/>
+      <c r="Q7" s="4"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="K8" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="L8" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="M8" s="6"/>
+      <c r="N8" s="6"/>
+      <c r="O8" s="6"/>
+      <c r="P8" s="6"/>
+      <c r="Q8" s="6"/>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:O9">
+    <sortCondition ref="A2:A9"/>
+  </sortState>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <conditionalFormatting sqref="B8:J8">
+    <cfRule type="duplicateValues" dxfId="8" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D8:H8">
+    <cfRule type="duplicateValues" dxfId="7" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R4:XFD4 A4:M4">
+    <cfRule type="duplicateValues" dxfId="6" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R6:XFD6 A6:L6">
+    <cfRule type="duplicateValues" dxfId="5" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A5:XFD5">
+    <cfRule type="duplicateValues" dxfId="4" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD224364-3393-400B-B6C8-18960E3F98D0}">
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="29.28515625" customWidth="1"/>
+    <col min="2" max="2" width="16.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:N8"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="29.28515625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="49.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="56" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="36.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="56.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="24.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="44.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="50.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="54.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="6"/>
+      <c r="N2" s="6"/>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4"/>
+      <c r="L3" s="4"/>
+      <c r="M3" s="4"/>
+      <c r="N3" s="4"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="K4" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="L4" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="M4" s="6"/>
+      <c r="N4" s="6"/>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="E4" t="s">
+      <c r="B5" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="L5" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="M5" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="N5" s="4" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="I6" s="6"/>
+      <c r="J6" s="6"/>
+      <c r="K6" s="6"/>
+      <c r="L6" s="6"/>
+      <c r="M6" s="6"/>
+      <c r="N6" s="6"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="4"/>
+      <c r="M7" s="4"/>
+      <c r="N7" s="4"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="J8" s="6"/>
+      <c r="K8" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F4" t="s">
+      <c r="L8" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="G4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H4" t="s">
-        <v>13</v>
-      </c>
-      <c r="I4" t="s">
-        <v>13</v>
-      </c>
-      <c r="J4" t="s">
-        <v>13</v>
-      </c>
-      <c r="K4" t="s">
-        <v>13</v>
-      </c>
-      <c r="L4" t="s">
-        <v>13</v>
-      </c>
-      <c r="M4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G5" t="s">
-        <v>13</v>
-      </c>
-      <c r="H5" t="s">
-        <v>13</v>
-      </c>
-      <c r="I5" t="s">
-        <v>13</v>
-      </c>
-      <c r="J5" t="s">
-        <v>13</v>
-      </c>
-      <c r="K5" t="s">
-        <v>13</v>
-      </c>
-      <c r="L5" t="s">
-        <v>13</v>
-      </c>
-      <c r="M5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G6" t="s">
-        <v>13</v>
-      </c>
-      <c r="H6" t="s">
-        <v>13</v>
-      </c>
-      <c r="I6" t="s">
-        <v>13</v>
-      </c>
-      <c r="J6" t="s">
-        <v>13</v>
-      </c>
-      <c r="K6" t="s">
-        <v>13</v>
-      </c>
-      <c r="L6" t="s">
-        <v>13</v>
-      </c>
-      <c r="M6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B7" t="s">
-        <v>30</v>
-      </c>
-      <c r="C7" t="s">
-        <v>31</v>
-      </c>
-      <c r="D7" t="s">
-        <v>32</v>
-      </c>
-      <c r="E7" t="s">
-        <v>33</v>
-      </c>
-      <c r="F7" t="s">
-        <v>34</v>
-      </c>
-      <c r="G7" t="s">
-        <v>35</v>
-      </c>
-      <c r="H7" t="s">
-        <v>36</v>
-      </c>
-      <c r="I7" t="s">
-        <v>13</v>
-      </c>
-      <c r="J7" t="s">
-        <v>13</v>
-      </c>
-      <c r="K7" t="s">
-        <v>13</v>
-      </c>
-      <c r="L7" t="s">
-        <v>13</v>
-      </c>
-      <c r="M7" t="s">
-        <v>13</v>
-      </c>
+      <c r="M8" s="6"/>
+      <c r="N8" s="6"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M5"/>
-  <sortState ref="A2:M7">
-    <sortCondition ref="A2:A7"/>
-  </sortState>
+  <conditionalFormatting sqref="B8:J8">
+    <cfRule type="duplicateValues" dxfId="2" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D8:H8">
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O4:XFD4 A4:L4">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
